--- a/output/pdf_financials_xlsx/LGO.xlsx
+++ b/output/pdf_financials_xlsx/LGO.xlsx
@@ -1267,16 +1267,16 @@
         <v>1.238064</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.819381</v>
+        <v>0.191717</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.886436</v>
+        <v>-3.886436</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>25.213</v>
+        <v>-25.213</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>11.576</v>
+        <v>-11.576</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-52.615</v>
@@ -1564,19 +1564,19 @@
         <v>-7.639752</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.840064</v>
+        <v>-0.840064</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.313832</v>
+        <v>-2.313832</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.886436</v>
+        <v>-3.886436</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>25.213</v>
+        <v>-25.213</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>11.576</v>
+        <v>-11.576</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-52.615</v>
@@ -1738,19 +1738,19 @@
         <v>-7.639752</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.840064</v>
+        <v>-0.840064</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.313832</v>
+        <v>-2.313832</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.886436</v>
+        <v>-3.886436</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>25.213</v>
+        <v>-25.213</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>11.576</v>
+        <v>-11.576</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-52.615</v>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>504.26</v>
+        <v>-504.26</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>89.046154</v>
+        <v>-89.046154</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>-101.182692</v>
@@ -2039,16 +2039,16 @@
         <v>1.238169</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.819514</v>
+        <v>0.19185</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.993575</v>
+        <v>-3.779297</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>25.256</v>
+        <v>-25.17</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.071</v>
+        <v>-11.081</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-52.615</v>
@@ -2155,16 +2155,16 @@
         <v>1.238169</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.821907</v>
+        <v>0.194243</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.00018</v>
+        <v>-3.772692</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>25.318</v>
+        <v>-25.108</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12.104</v>
+        <v>-11.048</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-52.556</v>
@@ -2285,16 +2285,16 @@
         <v>100</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>51.98902099667987</v>
+        <v>1306.899753282182</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -81419,13 +81419,13 @@
         </is>
       </c>
       <c r="I732" s="5" t="n">
-        <v>25.213</v>
+        <v>-25.213</v>
       </c>
       <c r="J732" s="5" t="n">
-        <v>11.576</v>
+        <v>-11.576</v>
       </c>
       <c r="K732" s="5" t="n">
-        <v>52.364</v>
+        <v>-52.364</v>
       </c>
       <c r="L732" t="inlineStr">
         <is>
@@ -98184,13 +98184,13 @@
         </is>
       </c>
       <c r="I901" s="5" t="n">
-        <v>30.783</v>
+        <v>-30.783</v>
       </c>
       <c r="J901" s="5" t="n">
-        <v>19.827</v>
+        <v>-19.827</v>
       </c>
       <c r="K901" s="5" t="n">
-        <v>54.214</v>
+        <v>-54.214</v>
       </c>
       <c r="L901" t="inlineStr">
         <is>
@@ -100082,10 +100082,10 @@
         </is>
       </c>
       <c r="H920" s="5" t="n">
-        <v>3.886436</v>
+        <v>-3.886436</v>
       </c>
       <c r="I920" s="5" t="n">
-        <v>25.212647</v>
+        <v>-25.212647</v>
       </c>
       <c r="J920" t="inlineStr">
         <is>
@@ -101179,13 +101179,13 @@
         <v>-7.639752</v>
       </c>
       <c r="F931" s="5" t="n">
-        <v>0.840064</v>
+        <v>-0.840064</v>
       </c>
       <c r="G931" s="5" t="n">
-        <v>2.313832</v>
+        <v>-2.313832</v>
       </c>
       <c r="H931" s="5" t="n">
-        <v>3.886436</v>
+        <v>-3.886436</v>
       </c>
       <c r="I931" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LGO.xlsx
+++ b/output/pdf_financials_xlsx/LGO.xlsx
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.054841</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>-0.000105</v>
@@ -1059,25 +1059,25 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.898</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>6.556</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.403</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>1.109</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>2.018</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.523</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="13">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>8.811752</v>
+        <v>8.866593</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>1.238169</v>
@@ -2063,25 +2063,25 @@
         <v>-11.793</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>315.956</v>
+        <v>315.058</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-36.212</v>
+        <v>-42.768</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>31.759</v>
+        <v>31.356</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.039</v>
+        <v>2.93</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-32.358</v>
+        <v>-34.376</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-50.565</v>
+        <v>-52.088</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-68.738</v>
+        <v>-69.021</v>
       </c>
     </row>
     <row r="28">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>8.811752</v>
+        <v>8.866593</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>1.238169</v>
@@ -2179,25 +2179,25 @@
         <v>21.432</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>346.997</v>
+        <v>346.099</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.515</v>
+        <v>-11.071</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>54.27</v>
+        <v>53.867</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>27.317</v>
+        <v>26.208</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.108</v>
+        <v>-5.126</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-21.89</v>
+        <v>-23.413</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-46.743</v>
+        <v>-47.026</v>
       </c>
     </row>
     <row r="30">
@@ -2251,25 +2251,25 @@
         <v>12.77821169428164</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>66.54910196292781</v>
+        <v>66.37687830231198</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-3.224723595120418</v>
+        <v>-7.907179384624174</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>27.3703853136978</v>
+        <v>27.16713738148073</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>11.91576045469813</v>
+        <v>11.43201120169596</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-1.564293048257535</v>
+        <v>-2.579976243683437</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-17.5232148575088</v>
+        <v>-18.74239513288504</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-42.53733380654673</v>
+        <v>-42.79487109485198</v>
       </c>
     </row>
     <row r="31">
@@ -2422,49 +2422,49 @@
         <v>0.908438</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.908438</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.424453</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.144</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>17.009</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>11.42</v>
+        <v>17.009</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.869</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.758</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>54.725</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>206.188</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>166.077</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>54.471</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>42.714</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>22.106</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>9.715999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2538,49 +2538,49 @@
         <v>0.908438</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.908438</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7.424453</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.144</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>17.009</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>11.42</v>
+        <v>17.009</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.869</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.758</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>54.725</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>206.188</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>166.077</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>54.471</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>42.714</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>22.106</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>9.715999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3234,49 +3234,49 @@
         <v>0.076131</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.984569</v>
+        <v>0.076131</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>83.078546</v>
+        <v>75.654093</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>58.748</v>
+        <v>56.604</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>17.686</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>23.275</v>
+        <v>17.686</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.612</v>
+        <v>5.743</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.291</v>
+        <v>2.533</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>60.403</v>
+        <v>5.678</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>209.56</v>
+        <v>3.372</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>172.528</v>
+        <v>6.451</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>90.97199999999999</v>
+        <v>7.182</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>68.94799999999999</v>
+        <v>14.477</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>49.96</v>
+        <v>7.246</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>36.008</v>
+        <v>13.902</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>17.474</v>
+        <v>7.758</v>
       </c>
     </row>
     <row r="49">
@@ -7665,16 +7665,16 @@
         <v>-124.994</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-24.788</v>
+        <v>-25.018</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-30</v>
+        <v>-30.569</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-35</v>
+        <v>-35.58</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>-27.075</v>
+        <v>-27.675</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>-92.229</v>
@@ -7723,16 +7723,16 @@
         <v>-124.994</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-24.788</v>
+        <v>-25.018</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-30</v>
+        <v>-30.569</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-35</v>
+        <v>-35.58</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>-27.075</v>
+        <v>-27.675</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>-92.229</v>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -23706,7 +23706,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -26732,7 +26732,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -29293,7 +29293,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -39462,7 +39462,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -41366,7 +41370,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -42964,7 +42972,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -80455,7 +80467,7 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E722" s="5" t="n">
@@ -97863,7 +97875,7 @@
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E898" s="5" t="n">

--- a/output/pdf_financials_xlsx/LGO.xlsx
+++ b/output/pdf_financials_xlsx/LGO.xlsx
@@ -2136,7 +2136,7 @@
         <v>29.25</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>28.675</v>
+        <v>1.092</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>21.995</v>
@@ -2194,7 +2194,7 @@
         <v>-5.126</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-23.413</v>
+        <v>-50.996</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-47.026</v>
@@ -2266,7 +2266,7 @@
         <v>-2.579976243683437</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-18.74239513288504</v>
+        <v>-40.82292667307076</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>-42.79487109485198</v>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.092</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>0</v>
@@ -40772,7 +40772,11 @@
           <t>Derecognition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LGO.xlsx
+++ b/output/pdf_financials_xlsx/LGO.xlsx
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.229616</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.152875</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1.002911</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.229616</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.164245</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.229616</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-1.164245</v>
@@ -1267,7 +1267,7 @@
         <v>1.238064</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.191717</v>
+        <v>-2.424943</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-3.886436</v>
@@ -1303,10 +1303,10 @@
         <v>4.039</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-32.358</v>
+        <v>-32.446</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-50.565</v>
+        <v>-47.752</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>-68.738</v>
@@ -1325,7 +1325,7 @@
         <v>-1.238064</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-2.505549</v>
+        <v>0.111111</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1361,10 +1361,10 @@
         <v>-6.265</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.813</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>-0</v>
@@ -2039,7 +2039,7 @@
         <v>1.238169</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.19185</v>
+        <v>-2.42481</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.779297</v>
@@ -2075,10 +2075,10 @@
         <v>2.93</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-34.376</v>
+        <v>-34.464</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-52.088</v>
+        <v>-49.275</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-69.021</v>
@@ -2155,7 +2155,7 @@
         <v>1.238169</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.194243</v>
+        <v>-2.422417</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.772692</v>
@@ -2191,10 +2191,10 @@
         <v>26.208</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.126</v>
+        <v>-5.214</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-50.996</v>
+        <v>-48.183</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-47.026</v>
@@ -2263,10 +2263,10 @@
         <v>11.43201120169596</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-2.579976243683437</v>
+        <v>-2.624267681343238</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-40.82292667307076</v>
+        <v>-38.57108549471662</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>-42.79487109485198</v>
@@ -2285,7 +2285,7 @@
         <v>100</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1306.899753282182</v>
+        <v>-4.582004607943362</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2321,10 +2321,10 @@
         <v>155.1126516464471</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.2712198730197867</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.890852739152287</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>-0</v>
@@ -4199,16 +4199,16 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>6.498433</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>3.038</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>6.071</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>12.162</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0</v>
@@ -4220,10 +4220,10 @@
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>24.107</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>7.72</v>
       </c>
       <c r="N64" s="3" t="n">
         <v>0</v>
@@ -4373,46 +4373,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.352104</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>3.820472</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>2.999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>3.456</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>3.107</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>2.363</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>2.962</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>3.122</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>4.531</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>6.228</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>19.553</v>
       </c>
     </row>
     <row r="68">
@@ -6875,13 +6875,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.037476</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.018873</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7494,7 +7494,7 @@
         <v>0</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-6.088</v>
       </c>
       <c r="P121" s="3" t="n">
         <v>0</v>
@@ -8283,13 +8283,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.037476</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.018873</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8341,13 +8341,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-2.430126</v>
+        <v>-2.467602</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.931609</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.378801</v>
+        <v>-1.397674</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-4.98014</v>
@@ -37783,7 +37783,11 @@
           <t>Deferred income tax expense (recovery) 17(a)</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -40976,7 +40980,11 @@
           <t>Deferred income tax recovery 17(a)</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -42576,7 +42584,11 @@
           <t>Deferred income tax recovery 16(a)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -43178,7 +43190,11 @@
           <t>Share repurchase 12</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -45847,7 +45863,11 @@
           <t>Deferred income tax expense (recovery) 16(a)</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -48069,7 +48089,11 @@
           <t>Deferred income tax recovery 15(a)</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -70015,7 +70039,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D618" t="inlineStr"/>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E618" t="inlineStr">
         <is>
           <t>-</t>
@@ -76576,7 +76604,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E683" s="5" t="n">
         <v>-0.037476</v>
       </c>
@@ -82870,7 +82902,11 @@
           <t>Income tax recovery (expense) 17(a)</t>
         </is>
       </c>
-      <c r="D747" t="inlineStr"/>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E747" t="inlineStr">
         <is>
           <t>-</t>
@@ -101085,7 +101121,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D930" t="inlineStr"/>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E930" t="inlineStr">
         <is>
           <t>-</t>
@@ -101588,7 +101628,11 @@
           <t>General office expenses</t>
         </is>
       </c>
-      <c r="D935" t="inlineStr"/>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E935" s="5" t="n">
         <v>0.229616</v>
       </c>
